--- a/2026/ILLIA/Febrero/ILLIA-Febrero.xlsx
+++ b/2026/ILLIA/Febrero/ILLIA-Febrero.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ILLIA\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C61A56D-E577-46A2-8F5F-3DF4A0921C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705B488A-3662-472A-80D7-730C5D16EADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="189">
   <si>
     <t>TELEFONO: 11 5320-2676</t>
   </si>
@@ -534,9 +534,6 @@
     <t>Sra. Fernanda Suplencia de Sra. Ana - Diferencia</t>
   </si>
   <si>
-    <t>VTO 13/03</t>
-  </si>
-  <si>
     <t>Sueldo Ana encargada FEBRERO</t>
   </si>
   <si>
@@ -592,6 +589,12 @@
   </si>
   <si>
     <t>CUIT: 30-71612269-3 - PERÍODO: FEBRERO - HORARIOS DE ATENCION: LUNES A VIERNES 10 a 15HS</t>
+  </si>
+  <si>
+    <t>No se debito</t>
+  </si>
+  <si>
+    <t>VTO 16/03</t>
   </si>
 </sst>
 </file>
@@ -610,7 +613,7 @@
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,14 +844,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -979,12 +976,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFB8CCE4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1568,7 +1559,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="27"/>
   </cellStyleXfs>
-  <cellXfs count="281">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1882,22 +1873,6 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="8" fillId="23" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="15" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="15" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="21" fillId="14" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="14" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1906,46 +1881,25 @@
     <xf numFmtId="164" fontId="21" fillId="18" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="18" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="35" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="35" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="35" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="35" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1973,13 +1927,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1987,12 +1967,8 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2001,15 +1977,25 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="28" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2325,11 +2311,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="188"/>
-      <c r="B3" s="247" t="s">
+      <c r="B3" s="223" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="248"/>
-      <c r="D3" s="248"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
       <c r="E3" s="190"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -2337,9 +2323,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="188"/>
-      <c r="B4" s="249"/>
-      <c r="C4" s="249"/>
-      <c r="D4" s="249"/>
+      <c r="B4" s="225"/>
+      <c r="C4" s="225"/>
+      <c r="D4" s="225"/>
       <c r="E4" s="190"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -2361,7 +2347,7 @@
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="193" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="194"/>
@@ -2373,13 +2359,13 @@
       <c r="I6" s="130"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="256" t="s">
+      <c r="A7" s="235" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="257"/>
-      <c r="C7" s="257"/>
-      <c r="D7" s="257"/>
-      <c r="E7" s="258"/>
+      <c r="B7" s="236"/>
+      <c r="C7" s="236"/>
+      <c r="D7" s="236"/>
+      <c r="E7" s="237"/>
       <c r="F7" s="5"/>
       <c r="G7" s="131"/>
       <c r="H7" s="131"/>
@@ -2392,10 +2378,10 @@
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="253" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="239"/>
+      <c r="B9" s="230" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="231"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2404,8 +2390,8 @@
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="239"/>
-      <c r="C10" s="239"/>
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2414,8 +2400,8 @@
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="239"/>
-      <c r="C11" s="239"/>
+      <c r="B11" s="231"/>
+      <c r="C11" s="231"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2434,43 +2420,43 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="259" t="s">
+      <c r="A14" s="238" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="239"/>
-      <c r="C14" s="239"/>
-      <c r="D14" s="239"/>
-      <c r="E14" s="239"/>
+      <c r="B14" s="231"/>
+      <c r="C14" s="231"/>
+      <c r="D14" s="231"/>
+      <c r="E14" s="231"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="239"/>
-      <c r="B15" s="239"/>
-      <c r="C15" s="239"/>
-      <c r="D15" s="239"/>
-      <c r="E15" s="239"/>
+      <c r="A15" s="231"/>
+      <c r="B15" s="231"/>
+      <c r="C15" s="231"/>
+      <c r="D15" s="231"/>
+      <c r="E15" s="231"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="239"/>
-      <c r="B16" s="239"/>
-      <c r="C16" s="239"/>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
+      <c r="A16" s="231"/>
+      <c r="B16" s="231"/>
+      <c r="C16" s="231"/>
+      <c r="D16" s="231"/>
+      <c r="E16" s="231"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="239"/>
-      <c r="B17" s="239"/>
-      <c r="C17" s="239"/>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239"/>
+      <c r="A17" s="231"/>
+      <c r="B17" s="231"/>
+      <c r="C17" s="231"/>
+      <c r="D17" s="231"/>
+      <c r="E17" s="231"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
@@ -2513,12 +2499,12 @@
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="221">
-        <v>805818.6</v>
+      <c r="D23" s="269">
+        <v>819241.2</v>
       </c>
       <c r="E23" s="13"/>
     </row>
@@ -2526,7 +2512,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="221"/>
+      <c r="D24" s="269"/>
       <c r="E24" s="13"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2554,7 +2540,7 @@
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="221"/>
+      <c r="D25" s="269"/>
       <c r="E25" s="13"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2584,8 +2570,8 @@
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
-      <c r="D26" s="221">
-        <v>-199940.12</v>
+      <c r="D26" s="269">
+        <v>-202762.2</v>
       </c>
       <c r="E26" s="13"/>
     </row>
@@ -2595,9 +2581,7 @@
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
-      <c r="D27" s="221">
-        <v>0.52</v>
-      </c>
+      <c r="D27" s="269"/>
       <c r="E27" s="13"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -2625,7 +2609,7 @@
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
-      <c r="D28" s="221"/>
+      <c r="D28" s="269"/>
       <c r="E28" s="13"/>
       <c r="F28" s="129"/>
       <c r="G28" s="129"/>
@@ -2657,7 +2641,7 @@
       <c r="C29" s="14"/>
       <c r="D29" s="147">
         <f>SUM(D23:D28)</f>
-        <v>605879</v>
+        <v>616479</v>
       </c>
       <c r="E29" s="15"/>
       <c r="F29" s="1"/>
@@ -2683,10 +2667,10 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="262" t="s">
+      <c r="A30" s="241" t="s">
         <v>167</v>
       </c>
-      <c r="B30" s="263"/>
+      <c r="B30" s="242"/>
       <c r="C30" s="13"/>
       <c r="D30" s="148"/>
       <c r="E30" s="13"/>
@@ -2762,7 +2746,7 @@
       <c r="D33" s="150"/>
       <c r="E33" s="17">
         <f>D29+D32</f>
-        <v>605879</v>
+        <v>616479</v>
       </c>
       <c r="F33" s="18"/>
     </row>
@@ -2801,10 +2785,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="167" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="13"/>
-      <c r="D35" s="222">
+      <c r="D35" s="270">
         <v>45000</v>
       </c>
       <c r="E35" s="21"/>
@@ -2835,10 +2819,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="167" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C36" s="13"/>
-      <c r="D36" s="223">
+      <c r="D36" s="269">
         <v>143100</v>
       </c>
       <c r="E36" s="21"/>
@@ -2910,16 +2894,16 @@
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="254" t="s">
+      <c r="A39" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="243"/>
+      <c r="B39" s="233"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="216">
+      <c r="D39" s="154">
         <v>63658.9</v>
       </c>
       <c r="E39" s="32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F39" s="1"/>
     </row>
@@ -2980,27 +2964,27 @@
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="29"/>
-      <c r="D43" s="217">
+      <c r="D43" s="271">
         <v>449693.05</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="13"/>
-      <c r="D44" s="215">
+      <c r="D44" s="156">
         <v>36261.839999999997</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -3033,7 +3017,7 @@
         <v>22</v>
       </c>
       <c r="C45" s="13"/>
-      <c r="D45" s="216">
+      <c r="D45" s="154">
         <v>108494.58</v>
       </c>
       <c r="E45" s="32" t="str">
@@ -3050,13 +3034,10 @@
       </c>
       <c r="B46" s="134"/>
       <c r="C46" s="134"/>
-      <c r="D46" s="214">
-        <v>180000</v>
-      </c>
-      <c r="E46" s="213" t="str">
-        <f>E45</f>
-        <v>Debito 12/02</v>
-      </c>
+      <c r="D46" s="214" t="s">
+        <v>187</v>
+      </c>
+      <c r="E46" s="213"/>
       <c r="F46" s="129"/>
       <c r="G46" s="129"/>
       <c r="H46" s="129"/>
@@ -3070,7 +3051,7 @@
         <v>23</v>
       </c>
       <c r="C47" s="134"/>
-      <c r="D47" s="218">
+      <c r="D47" s="214">
         <v>4029.09</v>
       </c>
       <c r="E47" s="33" t="str">
@@ -3090,7 +3071,7 @@
       <c r="D48" s="157"/>
       <c r="E48" s="26">
         <f>SUM(D42:D47)</f>
-        <v>778478.55999999994</v>
+        <v>598478.55999999994</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -3127,16 +3108,16 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="244" t="s">
-        <v>172</v>
-      </c>
-      <c r="B50" s="255"/>
+      <c r="A50" s="226" t="s">
+        <v>171</v>
+      </c>
+      <c r="B50" s="234"/>
       <c r="C50" s="13"/>
-      <c r="D50" s="220">
+      <c r="D50" s="272">
         <v>125300</v>
       </c>
       <c r="E50" s="137" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -3161,18 +3142,18 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" s="130" customFormat="1" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="264" t="s">
-        <v>177</v>
-      </c>
-      <c r="B51" s="265"/>
+      <c r="A51" s="243" t="s">
+        <v>176</v>
+      </c>
+      <c r="B51" s="244"/>
       <c r="C51" s="13"/>
-      <c r="D51" s="220">
+      <c r="D51" s="272">
         <v>53249.08</v>
       </c>
       <c r="E51" s="137" t="s">
-        <v>176</v>
-      </c>
-      <c r="F51" s="225"/>
+        <v>175</v>
+      </c>
+      <c r="F51" s="215"/>
       <c r="G51" s="129"/>
       <c r="H51" s="129"/>
       <c r="I51" s="129"/>
@@ -3195,16 +3176,16 @@
       <c r="Z51" s="129"/>
     </row>
     <row r="52" spans="1:26" s="130" customFormat="1" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="264" t="s">
-        <v>178</v>
-      </c>
-      <c r="B52" s="265"/>
+      <c r="A52" s="243" t="s">
+        <v>177</v>
+      </c>
+      <c r="B52" s="244"/>
       <c r="C52" s="13"/>
-      <c r="D52" s="220">
+      <c r="D52" s="272">
         <v>53249.08</v>
       </c>
       <c r="E52" s="137" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F52" s="129"/>
       <c r="G52" s="129"/>
@@ -3234,11 +3215,11 @@
       </c>
       <c r="B53" s="142"/>
       <c r="C53" s="13"/>
-      <c r="D53" s="220">
+      <c r="D53" s="272">
         <v>50000</v>
       </c>
       <c r="E53" s="137" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -3268,27 +3249,27 @@
       </c>
       <c r="B54" s="119"/>
       <c r="C54" s="35"/>
-      <c r="D54" s="224">
+      <c r="D54" s="273">
         <v>27403.45</v>
       </c>
       <c r="E54" s="137" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F54" s="36"/>
       <c r="G54" s="36"/>
       <c r="H54" s="36"/>
     </row>
     <row r="55" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="244" t="s">
-        <v>173</v>
-      </c>
-      <c r="B55" s="243"/>
+      <c r="A55" s="226" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" s="233"/>
       <c r="C55" s="20"/>
-      <c r="D55" s="219">
+      <c r="D55" s="274">
         <v>18355.59</v>
       </c>
       <c r="E55" s="137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F55" s="25"/>
       <c r="G55" s="25"/>
@@ -3313,12 +3294,12 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="244" t="s">
+      <c r="A56" s="226" t="s">
         <v>154</v>
       </c>
-      <c r="B56" s="243"/>
+      <c r="B56" s="233"/>
       <c r="C56" s="20"/>
-      <c r="D56" s="219">
+      <c r="D56" s="274">
         <v>180652.41</v>
       </c>
       <c r="E56" s="137"/>
@@ -3337,8 +3318,8 @@
       <c r="H57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="242"/>
-      <c r="B58" s="243"/>
+      <c r="A58" s="248"/>
+      <c r="B58" s="233"/>
       <c r="C58" s="13"/>
       <c r="D58" s="154"/>
       <c r="E58" s="34"/>
@@ -3393,11 +3374,11 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="244"/>
-      <c r="B60" s="250"/>
+      <c r="A60" s="226"/>
+      <c r="B60" s="227"/>
       <c r="C60" s="39"/>
-      <c r="D60" s="240"/>
-      <c r="E60" s="260"/>
+      <c r="D60" s="246"/>
+      <c r="E60" s="239"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -3421,11 +3402,11 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="251"/>
-      <c r="B61" s="252"/>
+      <c r="A61" s="228"/>
+      <c r="B61" s="229"/>
       <c r="C61" s="39"/>
-      <c r="D61" s="241"/>
-      <c r="E61" s="261"/>
+      <c r="D61" s="247"/>
+      <c r="E61" s="240"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -3449,8 +3430,8 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="244"/>
-      <c r="B62" s="243"/>
+      <c r="A62" s="226"/>
+      <c r="B62" s="233"/>
       <c r="C62" s="13"/>
       <c r="D62" s="158"/>
       <c r="E62" s="40"/>
@@ -3477,8 +3458,8 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="244"/>
-      <c r="B63" s="243"/>
+      <c r="A63" s="226"/>
+      <c r="B63" s="233"/>
       <c r="C63" s="13"/>
       <c r="D63" s="158"/>
       <c r="E63" s="40"/>
@@ -3505,8 +3486,8 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="244"/>
-      <c r="B64" s="243"/>
+      <c r="A64" s="226"/>
+      <c r="B64" s="233"/>
       <c r="C64" s="13"/>
       <c r="D64" s="158"/>
       <c r="E64" s="34"/>
@@ -3540,8 +3521,8 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="244"/>
-      <c r="B66" s="243"/>
+      <c r="A66" s="226"/>
+      <c r="B66" s="233"/>
       <c r="C66" s="13"/>
       <c r="D66" s="158"/>
       <c r="E66" s="34"/>
@@ -3596,8 +3577,8 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="244"/>
-      <c r="B68" s="243"/>
+      <c r="A68" s="226"/>
+      <c r="B68" s="233"/>
       <c r="C68" s="13"/>
       <c r="D68" s="158"/>
       <c r="E68" s="43"/>
@@ -3624,8 +3605,8 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="244"/>
-      <c r="B69" s="243"/>
+      <c r="A69" s="226"/>
+      <c r="B69" s="233"/>
       <c r="C69" s="13"/>
       <c r="D69" s="158"/>
       <c r="E69" s="43"/>
@@ -3652,8 +3633,8 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="245"/>
-      <c r="B70" s="243"/>
+      <c r="A70" s="249"/>
+      <c r="B70" s="233"/>
       <c r="C70" s="44"/>
       <c r="D70" s="158"/>
       <c r="E70" s="43"/>
@@ -3706,24 +3687,24 @@
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
-      <c r="D73" s="215">
+      <c r="D73" s="156">
         <v>29100</v>
       </c>
       <c r="E73" s="137" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:26" s="130" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
-      <c r="D74" s="215">
+      <c r="D74" s="156">
         <v>55000</v>
       </c>
       <c r="E74" s="137" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3761,7 +3742,7 @@
     </row>
     <row r="76" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B76" s="48"/>
       <c r="C76" s="16"/>
@@ -3795,7 +3776,7 @@
       </c>
       <c r="B77" s="13"/>
       <c r="C77" s="13"/>
-      <c r="D77" s="237">
+      <c r="D77" s="275">
         <v>35494.9</v>
       </c>
       <c r="E77" s="49"/>
@@ -3827,7 +3808,7 @@
       </c>
       <c r="B78" s="13"/>
       <c r="C78" s="13"/>
-      <c r="D78" s="216">
+      <c r="D78" s="154">
         <v>45000</v>
       </c>
       <c r="E78" s="40"/>
@@ -3881,10 +3862,7 @@
       <c r="B81" s="52"/>
       <c r="C81" s="52"/>
       <c r="D81" s="53"/>
-      <c r="E81" s="54">
-        <f>3000000-2327529.53</f>
-        <v>672470.4700000002</v>
-      </c>
+      <c r="E81" s="54"/>
       <c r="F81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3905,7 +3883,7 @@
       <c r="D83" s="60"/>
       <c r="E83" s="61">
         <f>(SUM(E30:E81))</f>
-        <v>2981391.4400000004</v>
+        <v>2139520.9700000002</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="170"/>
@@ -4244,7 +4222,7 @@
       </c>
       <c r="B96" s="66">
         <f>E83</f>
-        <v>2981391.4400000004</v>
+        <v>2139520.9700000002</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -4277,7 +4255,7 @@
       </c>
       <c r="B97" s="66">
         <f>E83-E81</f>
-        <v>2308920.9700000002</v>
+        <v>2139520.9700000002</v>
       </c>
     </row>
     <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4361,17 +4339,17 @@
       <c r="E101" s="129"/>
     </row>
     <row r="102" spans="1:26" s="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="246" t="s">
+      <c r="A102" s="250" t="s">
         <v>157</v>
       </c>
-      <c r="B102" s="246"/>
+      <c r="B102" s="250"/>
       <c r="C102" s="129"/>
       <c r="D102" s="129"/>
       <c r="E102" s="129"/>
     </row>
     <row r="103" spans="1:26" s="130" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="246"/>
-      <c r="B103" s="246"/>
+      <c r="A103" s="250"/>
+      <c r="B103" s="250"/>
       <c r="C103" s="129"/>
       <c r="D103" s="129"/>
       <c r="E103" s="129"/>
@@ -4384,17 +4362,17 @@
       <c r="E104" s="1"/>
     </row>
     <row r="105" spans="1:26" s="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="246" t="s">
+      <c r="A105" s="250" t="s">
         <v>163</v>
       </c>
-      <c r="B105" s="246"/>
+      <c r="B105" s="250"/>
       <c r="C105" s="129"/>
       <c r="D105" s="129"/>
       <c r="E105" s="129"/>
     </row>
     <row r="106" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="246"/>
-      <c r="B106" s="246"/>
+      <c r="A106" s="250"/>
+      <c r="B106" s="250"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -4418,7 +4396,7 @@
         <v>42</v>
       </c>
       <c r="B109" s="182">
-        <v>4590921.2899999991</v>
+        <v>5470073.8999999985</v>
       </c>
       <c r="C109" s="68"/>
     </row>
@@ -4478,7 +4456,7 @@
       </c>
       <c r="B113" s="70">
         <f>-B97</f>
-        <v>-2308920.9700000002</v>
+        <v>-2139520.9700000002</v>
       </c>
       <c r="C113" s="67"/>
       <c r="D113" s="1"/>
@@ -4507,7 +4485,7 @@
     </row>
     <row r="114" spans="1:26" s="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B114" s="205">
         <v>90000</v>
@@ -4516,7 +4494,7 @@
     </row>
     <row r="115" spans="1:26" s="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B115" s="205">
         <f>228000-132000</f>
@@ -4530,7 +4508,7 @@
       </c>
       <c r="B116" s="74">
         <f>SUM(B109:B115)</f>
-        <v>5577515.1799999997</v>
+        <v>6626067.7899999972</v>
       </c>
       <c r="C116" s="75"/>
     </row>
@@ -4697,16 +4675,16 @@
     <row r="126" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="127" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="238" t="s">
+      <c r="A128" s="245" t="s">
         <v>51</v>
       </c>
-      <c r="B128" s="239"/>
-      <c r="C128" s="239"/>
+      <c r="B128" s="231"/>
+      <c r="C128" s="231"/>
     </row>
     <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="239"/>
-      <c r="B129" s="239"/>
-      <c r="C129" s="239"/>
+      <c r="A129" s="231"/>
+      <c r="B129" s="231"/>
+      <c r="C129" s="231"/>
     </row>
     <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="13"/>
@@ -5666,6 +5644,18 @@
     <sortCondition ref="E39:E40"/>
   </sortState>
   <mergeCells count="25">
+    <mergeCell ref="A128:C129"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A102:B103"/>
+    <mergeCell ref="A105:B106"/>
     <mergeCell ref="B3:D4"/>
     <mergeCell ref="A60:B61"/>
     <mergeCell ref="B9:C11"/>
@@ -5679,18 +5669,6 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A128:C129"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A102:B103"/>
-    <mergeCell ref="A105:B106"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5731,16 +5709,16 @@
       <c r="C1" s="86"/>
       <c r="D1" s="86"/>
       <c r="E1" s="86"/>
-      <c r="F1" s="273"/>
-      <c r="G1" s="239"/>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
-      <c r="K1" s="239"/>
-      <c r="L1" s="239"/>
-      <c r="M1" s="239"/>
-      <c r="N1" s="239"/>
-      <c r="O1" s="239"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
+      <c r="K1" s="231"/>
+      <c r="L1" s="231"/>
+      <c r="M1" s="231"/>
+      <c r="N1" s="231"/>
+      <c r="O1" s="231"/>
       <c r="P1" s="86"/>
       <c r="Q1" s="86"/>
     </row>
@@ -5765,7 +5743,7 @@
       <c r="M2" s="86"/>
       <c r="N2" s="86"/>
       <c r="O2" s="171">
-        <v>3000000</v>
+        <v>2139520.9700000002</v>
       </c>
       <c r="P2" s="88"/>
       <c r="Q2" s="88"/>
@@ -5793,80 +5771,80 @@
       <c r="Q3" s="90"/>
     </row>
     <row r="4" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="280" t="s">
+      <c r="A4" s="251" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="269" t="s">
+      <c r="B4" s="258" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="274" t="s">
+      <c r="C4" s="253" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="274" t="s">
+      <c r="D4" s="253" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="278" t="s">
+      <c r="E4" s="254" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="274" t="s">
+      <c r="F4" s="253" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="274" t="s">
+      <c r="G4" s="253" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="274" t="s">
+      <c r="H4" s="253" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="278" t="s">
+      <c r="I4" s="254" t="s">
         <v>62</v>
       </c>
-      <c r="J4" s="279" t="s">
+      <c r="J4" s="265" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="267" t="s">
+      <c r="K4" s="257" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="271" t="s">
+      <c r="L4" s="260" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="267" t="s">
+      <c r="M4" s="257" t="s">
         <v>66</v>
       </c>
-      <c r="N4" s="275" t="s">
+      <c r="N4" s="262" t="s">
         <v>67</v>
       </c>
       <c r="O4" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="P4" s="277" t="s">
+      <c r="P4" s="264" t="s">
         <v>69</v>
       </c>
-      <c r="Q4" s="271" t="s">
+      <c r="Q4" s="260" t="s">
         <v>70</v>
       </c>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="272"/>
-      <c r="B5" s="270"/>
-      <c r="C5" s="272"/>
-      <c r="D5" s="272"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="272"/>
-      <c r="G5" s="272"/>
-      <c r="H5" s="272"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="272"/>
-      <c r="M5" s="268"/>
-      <c r="N5" s="276"/>
+      <c r="A5" s="252"/>
+      <c r="B5" s="259"/>
+      <c r="C5" s="252"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="255"/>
+      <c r="F5" s="252"/>
+      <c r="G5" s="252"/>
+      <c r="H5" s="252"/>
+      <c r="I5" s="255"/>
+      <c r="J5" s="255"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="252"/>
+      <c r="M5" s="255"/>
+      <c r="N5" s="263"/>
       <c r="O5" s="92" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 13/03</v>
-      </c>
-      <c r="P5" s="270"/>
-      <c r="Q5" s="272"/>
+        <v>VTO 16/03</v>
+      </c>
+      <c r="P5" s="259"/>
+      <c r="Q5" s="252"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
@@ -5890,7 +5868,7 @@
       <c r="G6" s="95">
         <v>33000.01</v>
       </c>
-      <c r="H6" s="233">
+      <c r="H6" s="132">
         <f t="shared" ref="H6:H12" si="0">G6</f>
         <v>33000.01</v>
       </c>
@@ -5909,22 +5887,22 @@
       </c>
       <c r="M6" s="98">
         <f>O$2*F6%</f>
-        <v>33000</v>
+        <v>23534.730670000004</v>
       </c>
       <c r="N6" s="99">
         <v>0</v>
       </c>
       <c r="O6" s="100">
         <f>ROUND(SUM(J6:N6),0) + R6</f>
-        <v>33000.01</v>
+        <v>23535.01</v>
       </c>
       <c r="P6" s="99">
         <f t="shared" ref="P6:P36" si="3">ROUND(O6*6% + O6,0) + R6</f>
-        <v>34980.01</v>
+        <v>24947.01</v>
       </c>
       <c r="Q6" s="101">
         <f t="shared" ref="Q6:Q36" si="4">ROUND(O6*3%,0) + O6</f>
-        <v>33990.01</v>
+        <v>24241.01</v>
       </c>
       <c r="R6" s="57">
         <v>0.01</v>
@@ -5950,7 +5928,7 @@
       <c r="G7" s="138">
         <v>40194.019999999997</v>
       </c>
-      <c r="H7" s="233">
+      <c r="H7" s="132">
         <v>40200</v>
       </c>
       <c r="I7" s="97"/>
@@ -5968,22 +5946,22 @@
       </c>
       <c r="M7" s="98">
         <f t="shared" ref="M7:M34" si="6">O$2*F7%</f>
-        <v>27000.000000000004</v>
+        <v>19255.688730000005</v>
       </c>
       <c r="N7" s="140">
         <v>0</v>
       </c>
-      <c r="O7" s="226">
+      <c r="O7" s="216">
         <f t="shared" ref="O7:O34" si="7">ROUND(SUM(J7:N7),0) + R7</f>
-        <v>26994.02</v>
+        <v>19250.02</v>
       </c>
       <c r="P7" s="140">
         <f t="shared" si="3"/>
-        <v>28614.02</v>
-      </c>
-      <c r="Q7" s="227">
+        <v>20405.02</v>
+      </c>
+      <c r="Q7" s="217">
         <f t="shared" si="4"/>
-        <v>27804.02</v>
+        <v>19828.02</v>
       </c>
       <c r="R7" s="57">
         <f t="shared" ref="R7:R35" si="8">R6+0.01</f>
@@ -6013,7 +5991,7 @@
       <c r="G8" s="138">
         <v>24000.03</v>
       </c>
-      <c r="H8" s="233">
+      <c r="H8" s="132">
         <f>G8</f>
         <v>24000.03</v>
       </c>
@@ -6032,22 +6010,22 @@
       </c>
       <c r="M8" s="98">
         <f t="shared" si="6"/>
-        <v>24000</v>
+        <v>17116.16776</v>
       </c>
       <c r="N8" s="140">
         <v>0</v>
       </c>
-      <c r="O8" s="226">
+      <c r="O8" s="216">
         <f t="shared" si="7"/>
-        <v>24000.03</v>
+        <v>17116.03</v>
       </c>
       <c r="P8" s="140">
         <f t="shared" si="3"/>
-        <v>25440.03</v>
-      </c>
-      <c r="Q8" s="227">
+        <v>18143.03</v>
+      </c>
+      <c r="Q8" s="217">
         <f t="shared" si="4"/>
-        <v>24720.03</v>
+        <v>17629.03</v>
       </c>
       <c r="R8" s="57">
         <f t="shared" si="8"/>
@@ -6074,7 +6052,7 @@
       <c r="G9" s="138">
         <v>24000.04</v>
       </c>
-      <c r="H9" s="233">
+      <c r="H9" s="132">
         <f t="shared" si="0"/>
         <v>24000.04</v>
       </c>
@@ -6093,22 +6071,22 @@
       </c>
       <c r="M9" s="98">
         <f t="shared" si="6"/>
-        <v>24000</v>
+        <v>17116.16776</v>
       </c>
       <c r="N9" s="140">
         <v>0</v>
       </c>
-      <c r="O9" s="226">
+      <c r="O9" s="216">
         <f t="shared" si="7"/>
-        <v>24000.04</v>
+        <v>17116.04</v>
       </c>
       <c r="P9" s="140">
         <f t="shared" si="3"/>
-        <v>25440.04</v>
-      </c>
-      <c r="Q9" s="227">
+        <v>18143.04</v>
+      </c>
+      <c r="Q9" s="217">
         <f t="shared" si="4"/>
-        <v>24720.04</v>
+        <v>17629.04</v>
       </c>
       <c r="R9" s="57">
         <f t="shared" si="8"/>
@@ -6153,22 +6131,22 @@
       </c>
       <c r="M10" s="98">
         <f t="shared" si="6"/>
-        <v>15000</v>
+        <v>10697.604850000002</v>
       </c>
       <c r="N10" s="140">
         <v>0</v>
       </c>
-      <c r="O10" s="226">
+      <c r="O10" s="216">
         <f t="shared" si="7"/>
-        <v>46364.05</v>
+        <v>42061.05</v>
       </c>
       <c r="P10" s="140">
         <f t="shared" si="3"/>
-        <v>49146.05</v>
-      </c>
-      <c r="Q10" s="227">
+        <v>44585.05</v>
+      </c>
+      <c r="Q10" s="217">
         <f t="shared" si="4"/>
-        <v>47755.05</v>
+        <v>43323.05</v>
       </c>
       <c r="R10" s="57">
         <f t="shared" si="8"/>
@@ -6195,7 +6173,7 @@
       <c r="G11" s="138">
         <v>15000.06</v>
       </c>
-      <c r="H11" s="233">
+      <c r="H11" s="132">
         <f t="shared" si="0"/>
         <v>15000.06</v>
       </c>
@@ -6214,22 +6192,22 @@
       </c>
       <c r="M11" s="98">
         <f t="shared" si="6"/>
-        <v>15000</v>
+        <v>10697.604850000002</v>
       </c>
       <c r="N11" s="140">
         <v>0</v>
       </c>
-      <c r="O11" s="226">
+      <c r="O11" s="216">
         <f t="shared" si="7"/>
-        <v>15000.06</v>
+        <v>10698.06</v>
       </c>
       <c r="P11" s="140">
         <f t="shared" si="3"/>
-        <v>15900.06</v>
-      </c>
-      <c r="Q11" s="227">
+        <v>11340.06</v>
+      </c>
+      <c r="Q11" s="217">
         <f t="shared" si="4"/>
-        <v>15450.06</v>
+        <v>11019.06</v>
       </c>
       <c r="R11" s="57">
         <f t="shared" si="8"/>
@@ -6258,7 +6236,7 @@
       <c r="G12" s="138">
         <v>15000.07</v>
       </c>
-      <c r="H12" s="233">
+      <c r="H12" s="132">
         <f t="shared" si="0"/>
         <v>15000.07</v>
       </c>
@@ -6277,22 +6255,22 @@
       </c>
       <c r="M12" s="98">
         <f t="shared" si="6"/>
-        <v>15000</v>
+        <v>10697.604850000002</v>
       </c>
       <c r="N12" s="140">
         <v>0</v>
       </c>
-      <c r="O12" s="226">
+      <c r="O12" s="216">
         <f t="shared" si="7"/>
-        <v>15000.07</v>
+        <v>10698.07</v>
       </c>
       <c r="P12" s="140">
         <f t="shared" si="3"/>
-        <v>15900.07</v>
-      </c>
-      <c r="Q12" s="227">
+        <v>11340.07</v>
+      </c>
+      <c r="Q12" s="217">
         <f t="shared" si="4"/>
-        <v>15450.07</v>
+        <v>11019.07</v>
       </c>
       <c r="R12" s="57">
         <f t="shared" si="8"/>
@@ -6321,7 +6299,7 @@
       <c r="G13" s="201">
         <v>132000.07999999999</v>
       </c>
-      <c r="H13" s="235">
+      <c r="H13" s="266">
         <f>228000-RESUMEN!B115</f>
         <v>132000</v>
       </c>
@@ -6340,20 +6318,20 @@
       </c>
       <c r="M13" s="203">
         <f t="shared" si="6"/>
-        <v>132000</v>
+        <v>94138.922680000018</v>
       </c>
       <c r="N13" s="204"/>
-      <c r="O13" s="228">
+      <c r="O13" s="218">
         <f t="shared" si="7"/>
-        <v>132000.07999999999</v>
+        <v>94139.08</v>
       </c>
       <c r="P13" s="204">
         <f t="shared" si="3"/>
-        <v>139920.07999999999</v>
-      </c>
-      <c r="Q13" s="229">
+        <v>99787.08</v>
+      </c>
+      <c r="Q13" s="219">
         <f t="shared" si="4"/>
-        <v>135960.07999999999</v>
+        <v>96963.08</v>
       </c>
       <c r="R13" s="57">
         <f t="shared" si="8"/>
@@ -6381,7 +6359,7 @@
       <c r="G14" s="95">
         <v>135000.09</v>
       </c>
-      <c r="H14" s="233">
+      <c r="H14" s="132">
         <f>159000-H9</f>
         <v>134999.96</v>
       </c>
@@ -6400,22 +6378,22 @@
       </c>
       <c r="M14" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N14" s="99">
         <v>0</v>
       </c>
       <c r="O14" s="100">
         <f t="shared" si="7"/>
-        <v>135000.09</v>
+        <v>96279.09</v>
       </c>
       <c r="P14" s="99">
         <f t="shared" si="3"/>
-        <v>143100.09</v>
+        <v>102056.09</v>
       </c>
       <c r="Q14" s="101">
         <f t="shared" si="4"/>
-        <v>139050.09</v>
+        <v>99167.09</v>
       </c>
       <c r="R14" s="57">
         <f t="shared" si="8"/>
@@ -6448,7 +6426,7 @@
       <c r="G15" s="95">
         <v>143469.1</v>
       </c>
-      <c r="H15" s="236">
+      <c r="H15" s="267">
         <f>G15</f>
         <v>143469.1</v>
       </c>
@@ -6467,22 +6445,22 @@
       </c>
       <c r="M15" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N15" s="99">
         <v>0</v>
       </c>
       <c r="O15" s="100">
         <f t="shared" si="7"/>
-        <v>135000.1</v>
+        <v>96278.1</v>
       </c>
       <c r="P15" s="99">
         <f t="shared" si="3"/>
-        <v>143100.1</v>
+        <v>102055.1</v>
       </c>
       <c r="Q15" s="101">
         <f t="shared" si="4"/>
-        <v>139050.1</v>
+        <v>99166.1</v>
       </c>
       <c r="R15" s="57">
         <f t="shared" si="8"/>
@@ -6512,7 +6490,7 @@
       <c r="G16" s="95">
         <v>93000.11</v>
       </c>
-      <c r="H16" s="233">
+      <c r="H16" s="132">
         <f>G16</f>
         <v>93000.11</v>
       </c>
@@ -6531,22 +6509,22 @@
       </c>
       <c r="M16" s="98">
         <f t="shared" si="6"/>
-        <v>93000</v>
+        <v>66325.150070000003</v>
       </c>
       <c r="N16" s="99">
         <v>0</v>
       </c>
       <c r="O16" s="100">
         <f t="shared" si="7"/>
-        <v>93000.11</v>
+        <v>66325.11</v>
       </c>
       <c r="P16" s="99">
         <f t="shared" si="3"/>
-        <v>98580.11</v>
+        <v>70305.11</v>
       </c>
       <c r="Q16" s="101">
         <f t="shared" si="4"/>
-        <v>95790.11</v>
+        <v>68315.11</v>
       </c>
       <c r="R16" s="57">
         <f t="shared" si="8"/>
@@ -6592,22 +6570,22 @@
       </c>
       <c r="M17" s="139">
         <f t="shared" si="6"/>
-        <v>132000</v>
+        <v>94138.922680000018</v>
       </c>
       <c r="N17" s="140">
         <v>0</v>
       </c>
-      <c r="O17" s="226">
+      <c r="O17" s="216">
         <f t="shared" si="7"/>
-        <v>795297.12</v>
+        <v>757436.12</v>
       </c>
       <c r="P17" s="140">
         <f t="shared" si="3"/>
-        <v>843015.12</v>
-      </c>
-      <c r="Q17" s="227">
+        <v>802882.12</v>
+      </c>
+      <c r="Q17" s="217">
         <f t="shared" si="4"/>
-        <v>819156.12</v>
+        <v>780159.12</v>
       </c>
       <c r="R17" s="57">
         <f t="shared" si="8"/>
@@ -6637,7 +6615,7 @@
       <c r="G18" s="138">
         <v>131068.13</v>
       </c>
-      <c r="H18" s="233">
+      <c r="H18" s="132">
         <v>135000</v>
       </c>
       <c r="I18" s="97"/>
@@ -6655,22 +6633,22 @@
       </c>
       <c r="M18" s="139">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N18" s="140">
         <v>0</v>
       </c>
-      <c r="O18" s="226">
+      <c r="O18" s="216">
         <f t="shared" si="7"/>
-        <v>131068.13</v>
+        <v>92347.13</v>
       </c>
       <c r="P18" s="140">
         <f t="shared" si="3"/>
-        <v>138932.13</v>
-      </c>
-      <c r="Q18" s="227">
+        <v>97888.13</v>
+      </c>
+      <c r="Q18" s="217">
         <f t="shared" si="4"/>
-        <v>135000.13</v>
+        <v>95117.13</v>
       </c>
       <c r="R18" s="57">
         <f t="shared" si="8"/>
@@ -6701,7 +6679,7 @@
       <c r="G19" s="95">
         <v>135000.14000000001</v>
       </c>
-      <c r="H19" s="233">
+      <c r="H19" s="132">
         <f>G19</f>
         <v>135000.14000000001</v>
       </c>
@@ -6720,22 +6698,22 @@
       </c>
       <c r="M19" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N19" s="99">
         <v>0</v>
       </c>
       <c r="O19" s="100">
         <f t="shared" si="7"/>
-        <v>135000.14000000001</v>
+        <v>96278.14</v>
       </c>
       <c r="P19" s="99">
         <f t="shared" si="3"/>
-        <v>143100.14000000001</v>
+        <v>102055.14</v>
       </c>
       <c r="Q19" s="101">
         <f t="shared" si="4"/>
-        <v>139050.14000000001</v>
+        <v>99166.14</v>
       </c>
       <c r="R19" s="57">
         <f t="shared" si="8"/>
@@ -6763,7 +6741,7 @@
       <c r="G20" s="95">
         <v>93000.15</v>
       </c>
-      <c r="H20" s="233">
+      <c r="H20" s="132">
         <f>G20</f>
         <v>93000.15</v>
       </c>
@@ -6782,22 +6760,22 @@
       </c>
       <c r="M20" s="98">
         <f t="shared" si="6"/>
-        <v>93000</v>
+        <v>66325.150070000003</v>
       </c>
       <c r="N20" s="99">
         <v>0</v>
       </c>
       <c r="O20" s="100">
         <f t="shared" si="7"/>
-        <v>93000.15</v>
+        <v>66325.149999999994</v>
       </c>
       <c r="P20" s="99">
         <f t="shared" si="3"/>
-        <v>98580.15</v>
+        <v>70305.149999999994</v>
       </c>
       <c r="Q20" s="101">
         <f t="shared" si="4"/>
-        <v>95790.15</v>
+        <v>68315.149999999994</v>
       </c>
       <c r="R20" s="57">
         <f t="shared" si="8"/>
@@ -6827,7 +6805,7 @@
       <c r="G21" s="95">
         <v>132000.16</v>
       </c>
-      <c r="H21" s="233">
+      <c r="H21" s="132">
         <f>G21</f>
         <v>132000.16</v>
       </c>
@@ -6846,22 +6824,22 @@
       </c>
       <c r="M21" s="98">
         <f t="shared" si="6"/>
-        <v>132000</v>
+        <v>94138.922680000018</v>
       </c>
       <c r="N21" s="99">
         <v>0</v>
       </c>
       <c r="O21" s="100">
         <f t="shared" si="7"/>
-        <v>132000.16</v>
+        <v>94139.16</v>
       </c>
       <c r="P21" s="99">
         <f t="shared" si="3"/>
-        <v>139920.16</v>
+        <v>99788.160000000003</v>
       </c>
       <c r="Q21" s="101">
         <f t="shared" si="4"/>
-        <v>135960.16</v>
+        <v>96963.16</v>
       </c>
       <c r="R21" s="57">
         <f t="shared" si="8"/>
@@ -6892,7 +6870,7 @@
       <c r="G22" s="96">
         <v>139050.17000000001</v>
       </c>
-      <c r="H22" s="233">
+      <c r="H22" s="132">
         <f>G22</f>
         <v>139050.17000000001</v>
       </c>
@@ -6911,22 +6889,22 @@
       </c>
       <c r="M22" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N22" s="99">
         <v>0</v>
       </c>
       <c r="O22" s="100">
         <f t="shared" si="7"/>
-        <v>135000.17000000001</v>
+        <v>96278.17</v>
       </c>
       <c r="P22" s="99">
         <f t="shared" si="3"/>
-        <v>143100.17000000001</v>
+        <v>102055.17</v>
       </c>
       <c r="Q22" s="101">
         <f t="shared" si="4"/>
-        <v>139050.17000000001</v>
+        <v>99166.17</v>
       </c>
       <c r="R22" s="57">
         <f t="shared" si="8"/>
@@ -6958,7 +6936,7 @@
       <c r="G23" s="138">
         <v>135000.18</v>
       </c>
-      <c r="H23" s="233">
+      <c r="H23" s="132">
         <v>139050</v>
       </c>
       <c r="I23" s="97"/>
@@ -6976,22 +6954,22 @@
       </c>
       <c r="M23" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N23" s="140">
         <v>0</v>
       </c>
-      <c r="O23" s="226">
+      <c r="O23" s="216">
         <f t="shared" si="7"/>
-        <v>130950.18</v>
+        <v>92229.18</v>
       </c>
       <c r="P23" s="140">
         <f t="shared" si="3"/>
-        <v>138807.18</v>
-      </c>
-      <c r="Q23" s="227">
+        <v>97763.18</v>
+      </c>
+      <c r="Q23" s="217">
         <f t="shared" si="4"/>
-        <v>134879.18</v>
+        <v>94996.18</v>
       </c>
       <c r="R23" s="57">
         <f t="shared" si="8"/>
@@ -7022,7 +7000,7 @@
       <c r="G24" s="95">
         <v>92986.19</v>
       </c>
-      <c r="H24" s="233">
+      <c r="H24" s="132">
         <f>117000-H8</f>
         <v>92999.97</v>
       </c>
@@ -7041,22 +7019,22 @@
       </c>
       <c r="M24" s="98">
         <f t="shared" si="6"/>
-        <v>93000</v>
+        <v>66325.150070000003</v>
       </c>
       <c r="N24" s="99">
         <v>0</v>
       </c>
       <c r="O24" s="100">
         <f t="shared" si="7"/>
-        <v>92986.19</v>
+        <v>66311.19</v>
       </c>
       <c r="P24" s="99">
         <f t="shared" si="3"/>
-        <v>98565.19</v>
+        <v>70290.19</v>
       </c>
       <c r="Q24" s="101">
         <f t="shared" si="4"/>
-        <v>95776.19</v>
+        <v>68300.19</v>
       </c>
       <c r="R24" s="57">
         <f t="shared" si="8"/>
@@ -7085,7 +7063,7 @@
       <c r="G25" s="138">
         <v>132000.20000000001</v>
       </c>
-      <c r="H25" s="233">
+      <c r="H25" s="132">
         <f>135000</f>
         <v>135000</v>
       </c>
@@ -7104,22 +7082,22 @@
       </c>
       <c r="M25" s="98">
         <f t="shared" si="6"/>
-        <v>132000</v>
+        <v>94138.922680000018</v>
       </c>
       <c r="N25" s="140">
         <v>0</v>
       </c>
-      <c r="O25" s="226">
+      <c r="O25" s="216">
         <f t="shared" si="7"/>
-        <v>129000.2</v>
+        <v>91139.199999999997</v>
       </c>
       <c r="P25" s="140">
         <f t="shared" si="3"/>
-        <v>136740.20000000001</v>
-      </c>
-      <c r="Q25" s="227">
+        <v>96608.2</v>
+      </c>
+      <c r="Q25" s="217">
         <f t="shared" si="4"/>
-        <v>132870.20000000001</v>
+        <v>93873.2</v>
       </c>
       <c r="R25" s="57">
         <f t="shared" si="8"/>
@@ -7154,7 +7132,7 @@
       <c r="G26" s="95">
         <v>135000.21</v>
       </c>
-      <c r="H26" s="233">
+      <c r="H26" s="132">
         <f>168000-H6</f>
         <v>134999.99</v>
       </c>
@@ -7173,22 +7151,22 @@
       </c>
       <c r="M26" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N26" s="99">
         <v>0</v>
       </c>
       <c r="O26" s="100">
         <f t="shared" si="7"/>
-        <v>135000.21</v>
+        <v>96279.21</v>
       </c>
       <c r="P26" s="99">
         <f t="shared" si="3"/>
-        <v>143100.21</v>
+        <v>102056.21</v>
       </c>
       <c r="Q26" s="101">
         <f t="shared" si="4"/>
-        <v>139050.21</v>
+        <v>99167.21</v>
       </c>
       <c r="R26" s="57">
         <f t="shared" si="8"/>
@@ -7219,7 +7197,7 @@
       <c r="G27" s="95">
         <v>352538.22</v>
       </c>
-      <c r="H27" s="233">
+      <c r="H27" s="132">
         <f>352538+15000-H12</f>
         <v>352537.93</v>
       </c>
@@ -7238,22 +7216,22 @@
       </c>
       <c r="M27" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N27" s="99">
         <v>0</v>
       </c>
       <c r="O27" s="100">
         <f t="shared" si="7"/>
-        <v>135000.22</v>
+        <v>96279.22</v>
       </c>
       <c r="P27" s="99">
         <f t="shared" si="3"/>
-        <v>143100.22</v>
+        <v>102056.22</v>
       </c>
       <c r="Q27" s="101">
         <f t="shared" si="4"/>
-        <v>139050.22</v>
+        <v>99167.22</v>
       </c>
       <c r="R27" s="57">
         <f t="shared" si="8"/>
@@ -7284,7 +7262,7 @@
       <c r="G28" s="138">
         <v>93000.23</v>
       </c>
-      <c r="H28" s="233">
+      <c r="H28" s="132">
         <f>G28</f>
         <v>93000.23</v>
       </c>
@@ -7303,22 +7281,22 @@
       </c>
       <c r="M28" s="139">
         <f t="shared" si="6"/>
-        <v>93000</v>
+        <v>66325.150070000003</v>
       </c>
       <c r="N28" s="140">
         <v>0</v>
       </c>
-      <c r="O28" s="226">
+      <c r="O28" s="216">
         <f t="shared" si="7"/>
-        <v>93000.23</v>
+        <v>66325.23</v>
       </c>
       <c r="P28" s="140">
         <f t="shared" si="3"/>
-        <v>98580.23</v>
-      </c>
-      <c r="Q28" s="227">
+        <v>70305.23</v>
+      </c>
+      <c r="Q28" s="217">
         <f t="shared" si="4"/>
-        <v>95790.23</v>
+        <v>68315.23</v>
       </c>
       <c r="R28" s="57">
         <f t="shared" si="8"/>
@@ -7346,7 +7324,7 @@
       <c r="G29" s="95">
         <v>203996.24</v>
       </c>
-      <c r="H29" s="233">
+      <c r="H29" s="132">
         <f>218996-H11</f>
         <v>203995.94</v>
       </c>
@@ -7365,22 +7343,22 @@
       </c>
       <c r="M29" s="98">
         <f t="shared" si="6"/>
-        <v>204000.00000000003</v>
+        <v>145487.42596000002</v>
       </c>
       <c r="N29" s="99">
         <v>0</v>
       </c>
       <c r="O29" s="100">
         <f t="shared" si="7"/>
-        <v>204000.24</v>
+        <v>145488.24</v>
       </c>
       <c r="P29" s="99">
         <f t="shared" si="3"/>
-        <v>216240.24</v>
+        <v>154218.23999999999</v>
       </c>
       <c r="Q29" s="101">
         <f t="shared" si="4"/>
-        <v>210120.24</v>
+        <v>149853.24</v>
       </c>
       <c r="R29" s="57">
         <f t="shared" si="8"/>
@@ -7408,7 +7386,7 @@
       <c r="G30" s="138">
         <v>213210.25</v>
       </c>
-      <c r="H30" s="233">
+      <c r="H30" s="132">
         <f>G30</f>
         <v>213210.25</v>
       </c>
@@ -7427,20 +7405,20 @@
       </c>
       <c r="M30" s="139">
         <f t="shared" si="6"/>
-        <v>207000.00000000003</v>
+        <v>147626.94693000003</v>
       </c>
       <c r="N30" s="140"/>
-      <c r="O30" s="226">
+      <c r="O30" s="216">
         <f t="shared" si="7"/>
-        <v>207000.25</v>
+        <v>147627.25</v>
       </c>
       <c r="P30" s="140">
         <f t="shared" si="3"/>
-        <v>219420.25</v>
-      </c>
-      <c r="Q30" s="227">
+        <v>156485.25</v>
+      </c>
+      <c r="Q30" s="217">
         <f t="shared" si="4"/>
-        <v>213210.25</v>
+        <v>152056.25</v>
       </c>
       <c r="R30" s="207">
         <f t="shared" si="8"/>
@@ -7472,7 +7450,7 @@
       <c r="G31" s="95">
         <v>135000.26</v>
       </c>
-      <c r="H31" s="233">
+      <c r="H31" s="132">
         <f>G31</f>
         <v>135000.26</v>
       </c>
@@ -7491,22 +7469,22 @@
       </c>
       <c r="M31" s="98">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N31" s="99">
         <v>0</v>
       </c>
       <c r="O31" s="100">
         <f t="shared" si="7"/>
-        <v>135000.26</v>
+        <v>96278.26</v>
       </c>
       <c r="P31" s="99">
         <f t="shared" si="3"/>
-        <v>143100.26</v>
+        <v>102055.26</v>
       </c>
       <c r="Q31" s="101">
         <f t="shared" si="4"/>
-        <v>139050.26</v>
+        <v>99166.26</v>
       </c>
       <c r="R31" s="57">
         <f t="shared" si="8"/>
@@ -7536,7 +7514,7 @@
       <c r="G32" s="95">
         <v>200444.27</v>
       </c>
-      <c r="H32" s="234">
+      <c r="H32" s="268">
         <v>93000</v>
       </c>
       <c r="I32" s="97"/>
@@ -7554,22 +7532,22 @@
       </c>
       <c r="M32" s="98">
         <f t="shared" si="6"/>
-        <v>93000</v>
+        <v>66325.150070000003</v>
       </c>
       <c r="N32" s="99">
         <v>0</v>
       </c>
       <c r="O32" s="100">
         <f t="shared" si="7"/>
-        <v>203668.27</v>
+        <v>176993.27</v>
       </c>
       <c r="P32" s="99">
         <f t="shared" si="3"/>
-        <v>215888.27</v>
+        <v>187613.27</v>
       </c>
       <c r="Q32" s="101">
         <f t="shared" si="4"/>
-        <v>209778.27</v>
+        <v>182303.27</v>
       </c>
       <c r="R32" s="57">
         <f t="shared" si="8"/>
@@ -7599,7 +7577,7 @@
       <c r="G33" s="176">
         <v>135000.28</v>
       </c>
-      <c r="H33" s="235">
+      <c r="H33" s="266">
         <f>225000-RESUMEN!B114</f>
         <v>135000</v>
       </c>
@@ -7615,20 +7593,20 @@
       </c>
       <c r="M33" s="178">
         <f t="shared" si="6"/>
-        <v>135000</v>
+        <v>96278.443650000001</v>
       </c>
       <c r="N33" s="179"/>
-      <c r="O33" s="230">
+      <c r="O33" s="220">
         <f t="shared" si="7"/>
-        <v>135000.28</v>
-      </c>
-      <c r="P33" s="231">
+        <v>96279.28</v>
+      </c>
+      <c r="P33" s="221">
         <f t="shared" si="3"/>
-        <v>143100.28</v>
-      </c>
-      <c r="Q33" s="232">
+        <v>102056.28</v>
+      </c>
+      <c r="Q33" s="222">
         <f t="shared" si="4"/>
-        <v>139050.28</v>
+        <v>99167.28</v>
       </c>
       <c r="R33" s="57">
         <f t="shared" si="8"/>
@@ -7656,7 +7634,7 @@
       <c r="G34" s="95">
         <v>93000.29</v>
       </c>
-      <c r="H34" s="233">
+      <c r="H34" s="132">
         <f>G34</f>
         <v>93000.29</v>
       </c>
@@ -7675,22 +7653,22 @@
       </c>
       <c r="M34" s="98">
         <f t="shared" si="6"/>
-        <v>93000</v>
+        <v>66325.150070000003</v>
       </c>
       <c r="N34" s="99">
         <v>0</v>
       </c>
       <c r="O34" s="100">
         <f t="shared" si="7"/>
-        <v>93000.29</v>
+        <v>66325.289999999994</v>
       </c>
       <c r="P34" s="99">
         <f t="shared" si="3"/>
-        <v>98580.29</v>
+        <v>70305.289999999994</v>
       </c>
       <c r="Q34" s="101">
         <f t="shared" si="4"/>
-        <v>95790.29</v>
+        <v>68315.289999999994</v>
       </c>
       <c r="R34" s="57">
         <f t="shared" si="8"/>
@@ -7816,7 +7794,7 @@
       </c>
       <c r="M37" s="111">
         <f t="shared" si="10"/>
-        <v>3000000</v>
+        <v>2139520.9700000002</v>
       </c>
       <c r="N37" s="112">
         <f t="shared" si="10"/>
@@ -7824,15 +7802,15 @@
       </c>
       <c r="O37" s="113">
         <f t="shared" si="10"/>
-        <v>3794331.3499999996</v>
+        <v>2933854.3499999987</v>
       </c>
       <c r="P37" s="113">
         <f t="shared" si="10"/>
-        <v>4021991.6499999994</v>
+        <v>3109893.6499999994</v>
       </c>
       <c r="Q37" s="113">
         <f t="shared" si="10"/>
-        <v>3908162.3499999996</v>
+        <v>3021867.3499999996</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7849,95 +7827,95 @@
       <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="266" t="s">
+      <c r="D40" s="256" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
-      <c r="M40" s="239"/>
-      <c r="N40" s="239"/>
-      <c r="O40" s="239"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="231"/>
+      <c r="O40" s="231"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="239"/>
-      <c r="E41" s="239"/>
-      <c r="F41" s="239"/>
-      <c r="G41" s="239"/>
-      <c r="H41" s="239"/>
-      <c r="I41" s="239"/>
-      <c r="J41" s="239"/>
-      <c r="K41" s="239"/>
-      <c r="L41" s="239"/>
-      <c r="M41" s="239"/>
-      <c r="N41" s="239"/>
-      <c r="O41" s="239"/>
+      <c r="D41" s="231"/>
+      <c r="E41" s="231"/>
+      <c r="F41" s="231"/>
+      <c r="G41" s="231"/>
+      <c r="H41" s="231"/>
+      <c r="I41" s="231"/>
+      <c r="J41" s="231"/>
+      <c r="K41" s="231"/>
+      <c r="L41" s="231"/>
+      <c r="M41" s="231"/>
+      <c r="N41" s="231"/>
+      <c r="O41" s="231"/>
       <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="239"/>
-      <c r="E42" s="239"/>
-      <c r="F42" s="239"/>
-      <c r="G42" s="239"/>
-      <c r="H42" s="239"/>
-      <c r="I42" s="239"/>
-      <c r="J42" s="239"/>
-      <c r="K42" s="239"/>
-      <c r="L42" s="239"/>
-      <c r="M42" s="239"/>
-      <c r="N42" s="239"/>
-      <c r="O42" s="239"/>
+      <c r="D42" s="231"/>
+      <c r="E42" s="231"/>
+      <c r="F42" s="231"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="231"/>
+      <c r="I42" s="231"/>
+      <c r="J42" s="231"/>
+      <c r="K42" s="231"/>
+      <c r="L42" s="231"/>
+      <c r="M42" s="231"/>
+      <c r="N42" s="231"/>
+      <c r="O42" s="231"/>
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="239"/>
-      <c r="E43" s="239"/>
-      <c r="F43" s="239"/>
-      <c r="G43" s="239"/>
-      <c r="H43" s="239"/>
-      <c r="I43" s="239"/>
-      <c r="J43" s="239"/>
-      <c r="K43" s="239"/>
-      <c r="L43" s="239"/>
-      <c r="M43" s="239"/>
-      <c r="N43" s="239"/>
-      <c r="O43" s="239"/>
+      <c r="D43" s="231"/>
+      <c r="E43" s="231"/>
+      <c r="F43" s="231"/>
+      <c r="G43" s="231"/>
+      <c r="H43" s="231"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="231"/>
+      <c r="L43" s="231"/>
+      <c r="M43" s="231"/>
+      <c r="N43" s="231"/>
+      <c r="O43" s="231"/>
       <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D44" s="239"/>
-      <c r="E44" s="239"/>
-      <c r="F44" s="239"/>
-      <c r="G44" s="239"/>
-      <c r="H44" s="239"/>
-      <c r="I44" s="239"/>
-      <c r="J44" s="239"/>
-      <c r="K44" s="239"/>
-      <c r="L44" s="239"/>
-      <c r="M44" s="239"/>
-      <c r="N44" s="239"/>
-      <c r="O44" s="239"/>
+      <c r="D44" s="231"/>
+      <c r="E44" s="231"/>
+      <c r="F44" s="231"/>
+      <c r="G44" s="231"/>
+      <c r="H44" s="231"/>
+      <c r="I44" s="231"/>
+      <c r="J44" s="231"/>
+      <c r="K44" s="231"/>
+      <c r="L44" s="231"/>
+      <c r="M44" s="231"/>
+      <c r="N44" s="231"/>
+      <c r="O44" s="231"/>
       <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D45" s="239"/>
-      <c r="E45" s="239"/>
-      <c r="F45" s="239"/>
-      <c r="G45" s="239"/>
-      <c r="H45" s="239"/>
-      <c r="I45" s="239"/>
-      <c r="J45" s="239"/>
-      <c r="K45" s="239"/>
-      <c r="L45" s="239"/>
-      <c r="M45" s="239"/>
-      <c r="N45" s="239"/>
-      <c r="O45" s="239"/>
+      <c r="D45" s="231"/>
+      <c r="E45" s="231"/>
+      <c r="F45" s="231"/>
+      <c r="G45" s="231"/>
+      <c r="H45" s="231"/>
+      <c r="I45" s="231"/>
+      <c r="J45" s="231"/>
+      <c r="K45" s="231"/>
+      <c r="L45" s="231"/>
+      <c r="M45" s="231"/>
+      <c r="N45" s="231"/>
+      <c r="O45" s="231"/>
       <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -13408,11 +13386,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -13426,6 +13399,11 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
